--- a/data/excel/ot_hh.xlsx
+++ b/data/excel/ot_hh.xlsx
@@ -38,6 +38,24 @@
   </x:si>
   <x:si>
     <x:t>RegistradoPor</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HoraInicio</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HoraTermino</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Comentario</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ValidadoSupervisor</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ValidadoPor</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ValidadoEnUtc</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -414,9 +432,15 @@
     <x:col min="6" max="6" width="11.139196" style="0" customWidth="1"/>
     <x:col min="7" max="7" width="13.139196" style="0" customWidth="1"/>
     <x:col min="8" max="8" width="13.710625" style="0" customWidth="1"/>
+    <x:col min="9" max="9" width="9.996339" style="0" customWidth="1"/>
+    <x:col min="10" max="10" width="12.853482" style="0" customWidth="1"/>
+    <x:col min="11" max="11" width="11.424911" style="0" customWidth="1"/>
+    <x:col min="12" max="12" width="18.424911" style="0" customWidth="1"/>
+    <x:col min="13" max="13" width="11.710625" style="0" customWidth="1"/>
+    <x:col min="14" max="14" width="13.996339" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:8">
+    <x:row r="1" spans="1:14">
       <x:c r="A1" s="1" t="s">
         <x:v>0</x:v>
       </x:c>
@@ -440,6 +464,24 @@
       </x:c>
       <x:c r="H1" s="1" t="s">
         <x:v>7</x:v>
+      </x:c>
+      <x:c r="I1" s="1" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="J1" s="1" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="K1" s="1" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="L1" s="1" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="M1" s="1" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="N1" s="1" t="s">
+        <x:v>13</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
